--- a/research/traditional_assets/database/data/ghana/ghana_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/ghana/ghana_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.238</v>
+        <v>0.231</v>
       </c>
       <c r="E2">
-        <v>0.238</v>
+        <v>0.248</v>
       </c>
       <c r="G2">
-        <v>0.1657579062159215</v>
+        <v>0.2194381169324222</v>
       </c>
       <c r="H2">
-        <v>0.1657579062159215</v>
+        <v>0.2194381169324222</v>
       </c>
       <c r="I2">
-        <v>0.1423118865866957</v>
+        <v>0.1442672741078208</v>
       </c>
       <c r="J2">
-        <v>0.1206186514403343</v>
+        <v>0.1207918300961932</v>
       </c>
       <c r="K2">
-        <v>11.8</v>
+        <v>9.33</v>
       </c>
       <c r="L2">
-        <v>0.064340239912759</v>
+        <v>0.07084282460136675</v>
       </c>
       <c r="M2">
-        <v>1.77</v>
+        <v>1.24</v>
       </c>
       <c r="N2">
-        <v>0.02246192893401015</v>
+        <v>0.02156521739130435</v>
       </c>
       <c r="O2">
-        <v>0.15</v>
+        <v>0.1329046087888532</v>
       </c>
       <c r="P2">
-        <v>1.77</v>
+        <v>1.24</v>
       </c>
       <c r="Q2">
-        <v>0.02246192893401015</v>
+        <v>0.02156521739130435</v>
       </c>
       <c r="R2">
-        <v>0.15</v>
+        <v>0.1329046087888532</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,70 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>38.4</v>
+        <v>20.4</v>
       </c>
       <c r="V2">
-        <v>0.4873096446700508</v>
+        <v>0.3547826086956521</v>
       </c>
       <c r="W2">
-        <v>0.1164856860809477</v>
+        <v>0.08835227272727274</v>
       </c>
       <c r="X2">
-        <v>0.1254564105094182</v>
+        <v>0.2656539013594726</v>
       </c>
       <c r="Y2">
-        <v>-0.008970724428470564</v>
+        <v>-0.1773016286321999</v>
       </c>
       <c r="Z2">
-        <v>4.072840328669777</v>
+        <v>1.789645332246229</v>
       </c>
       <c r="AA2">
-        <v>0.4912605079759563</v>
+        <v>0.2161745349051316</v>
       </c>
       <c r="AB2">
-        <v>0.1204729665191414</v>
+        <v>0.2565462865225929</v>
       </c>
       <c r="AC2">
-        <v>0.3707875414568148</v>
+        <v>-0.04037175161746129</v>
       </c>
       <c r="AD2">
-        <v>6.39</v>
+        <v>4.72</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6.39</v>
+        <v>4.72</v>
       </c>
       <c r="AG2">
-        <v>-32.01</v>
+        <v>-15.68</v>
       </c>
       <c r="AH2">
-        <v>0.07500880385021716</v>
+        <v>0.07585985213757634</v>
       </c>
       <c r="AI2">
-        <v>0.04503488617943478</v>
+        <v>0.049569418189456</v>
       </c>
       <c r="AJ2">
-        <v>-0.6841205385766189</v>
+        <v>-0.3749402199904352</v>
       </c>
       <c r="AK2">
-        <v>-0.3093052468837568</v>
+        <v>-0.2095696337877573</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.719</v>
       </c>
       <c r="AM2">
-        <v>-0.017</v>
+        <v>0.719</v>
       </c>
       <c r="AN2">
-        <v>0.2257950530035336</v>
+        <v>0.2313725490196079</v>
+      </c>
+      <c r="AO2">
+        <v>26.42559109874826</v>
       </c>
       <c r="AP2">
-        <v>-1.131095406360424</v>
+        <v>-0.7686274509803922</v>
       </c>
       <c r="AQ2">
-        <v>-1535.294117647059</v>
+        <v>26.42559109874826</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.238</v>
+        <v>0.231</v>
       </c>
       <c r="E3">
-        <v>0.238</v>
+        <v>0.248</v>
       </c>
       <c r="G3">
-        <v>0.1657579062159215</v>
+        <v>0.2194381169324222</v>
       </c>
       <c r="H3">
-        <v>0.1657579062159215</v>
+        <v>0.2194381169324222</v>
       </c>
       <c r="I3">
-        <v>0.1423118865866957</v>
+        <v>0.1442672741078208</v>
       </c>
       <c r="J3">
-        <v>0.1206186514403343</v>
+        <v>0.1207918300961932</v>
       </c>
       <c r="K3">
-        <v>11.8</v>
+        <v>9.33</v>
       </c>
       <c r="L3">
-        <v>0.064340239912759</v>
+        <v>0.07084282460136675</v>
       </c>
       <c r="M3">
-        <v>1.77</v>
+        <v>1.24</v>
       </c>
       <c r="N3">
-        <v>0.02246192893401015</v>
+        <v>0.02156521739130435</v>
       </c>
       <c r="O3">
-        <v>0.15</v>
+        <v>0.1329046087888532</v>
       </c>
       <c r="P3">
-        <v>1.77</v>
+        <v>1.24</v>
       </c>
       <c r="Q3">
-        <v>0.02246192893401015</v>
+        <v>0.02156521739130435</v>
       </c>
       <c r="R3">
-        <v>0.15</v>
+        <v>0.1329046087888532</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,70 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>38.4</v>
+        <v>20.4</v>
       </c>
       <c r="V3">
-        <v>0.4873096446700508</v>
+        <v>0.3547826086956521</v>
       </c>
       <c r="W3">
-        <v>0.1164856860809477</v>
+        <v>0.08835227272727274</v>
       </c>
       <c r="X3">
-        <v>0.1254564105094182</v>
+        <v>0.2656539013594726</v>
       </c>
       <c r="Y3">
-        <v>-0.008970724428470564</v>
+        <v>-0.1773016286321999</v>
       </c>
       <c r="Z3">
-        <v>4.072840328669777</v>
+        <v>1.789645332246229</v>
       </c>
       <c r="AA3">
-        <v>0.4912605079759563</v>
+        <v>0.2161745349051316</v>
       </c>
       <c r="AB3">
-        <v>0.1204729665191414</v>
+        <v>0.2565462865225929</v>
       </c>
       <c r="AC3">
-        <v>0.3707875414568148</v>
+        <v>-0.04037175161746129</v>
       </c>
       <c r="AD3">
-        <v>6.39</v>
+        <v>4.72</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.39</v>
+        <v>4.72</v>
       </c>
       <c r="AG3">
-        <v>-32.01</v>
+        <v>-15.68</v>
       </c>
       <c r="AH3">
-        <v>0.07500880385021716</v>
+        <v>0.07585985213757634</v>
       </c>
       <c r="AI3">
-        <v>0.04503488617943478</v>
+        <v>0.049569418189456</v>
       </c>
       <c r="AJ3">
-        <v>-0.6841205385766189</v>
+        <v>-0.3749402199904352</v>
       </c>
       <c r="AK3">
-        <v>-0.3093052468837568</v>
+        <v>-0.2095696337877573</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.719</v>
       </c>
       <c r="AM3">
-        <v>-0.017</v>
+        <v>0.719</v>
       </c>
       <c r="AN3">
-        <v>0.2257950530035336</v>
+        <v>0.2313725490196079</v>
+      </c>
+      <c r="AO3">
+        <v>26.42559109874826</v>
       </c>
       <c r="AP3">
-        <v>-1.131095406360424</v>
+        <v>-0.7686274509803922</v>
       </c>
       <c r="AQ3">
-        <v>-1535.294117647059</v>
+        <v>26.42559109874826</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/ghana/ghana_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/ghana/ghana_insurance_life.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.231</v>
+        <v>0.177</v>
       </c>
       <c r="E2">
-        <v>0.248</v>
+        <v>0.205</v>
       </c>
       <c r="G2">
-        <v>0.2194381169324222</v>
+        <v>0.08828828828828829</v>
       </c>
       <c r="H2">
-        <v>0.2194381169324222</v>
+        <v>0.08828828828828829</v>
       </c>
       <c r="I2">
-        <v>0.1442672741078208</v>
+        <v>0.07684684684684684</v>
       </c>
       <c r="J2">
-        <v>0.1207918300961932</v>
+        <v>0.06301441441441441</v>
       </c>
       <c r="K2">
-        <v>9.33</v>
+        <v>12.3</v>
       </c>
       <c r="L2">
-        <v>0.07084282460136675</v>
+        <v>0.1108108108108108</v>
       </c>
       <c r="M2">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
-        <v>0.02156521739130435</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="O2">
-        <v>0.1329046087888532</v>
+        <v>0.08943089430894309</v>
       </c>
       <c r="P2">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="Q2">
-        <v>0.02156521739130435</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="R2">
-        <v>0.1329046087888532</v>
+        <v>0.08943089430894309</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>20.4</v>
+        <v>38.6</v>
       </c>
       <c r="V2">
-        <v>0.3547826086956521</v>
+        <v>1.131964809384164</v>
       </c>
       <c r="W2">
-        <v>0.08835227272727274</v>
+        <v>0.1754636233951498</v>
       </c>
       <c r="X2">
-        <v>0.2656539013594726</v>
+        <v>0.1906774660719821</v>
       </c>
       <c r="Y2">
-        <v>-0.1773016286321999</v>
+        <v>-0.01521384267683232</v>
       </c>
       <c r="Z2">
-        <v>1.789645332246229</v>
+        <v>2.039691289966924</v>
       </c>
       <c r="AA2">
-        <v>0.2161745349051316</v>
+        <v>0.1285299522234473</v>
       </c>
       <c r="AB2">
-        <v>0.2565462865225929</v>
+        <v>0.1893554156546594</v>
       </c>
       <c r="AC2">
-        <v>-0.04037175161746129</v>
+        <v>-0.06082546343121206</v>
       </c>
       <c r="AD2">
-        <v>4.72</v>
+        <v>0.668</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.72</v>
+        <v>0.668</v>
       </c>
       <c r="AG2">
-        <v>-15.68</v>
+        <v>-37.932</v>
       </c>
       <c r="AH2">
-        <v>0.07585985213757634</v>
+        <v>0.01921306948918546</v>
       </c>
       <c r="AI2">
-        <v>0.049569418189456</v>
+        <v>0.00693176158060767</v>
       </c>
       <c r="AJ2">
-        <v>-0.3749402199904352</v>
+        <v>9.898747390396659</v>
       </c>
       <c r="AK2">
-        <v>-0.2095696337877573</v>
+        <v>-0.6566265060240964</v>
       </c>
       <c r="AL2">
-        <v>0.719</v>
+        <v>0.003</v>
       </c>
       <c r="AM2">
-        <v>0.719</v>
+        <v>0.003</v>
       </c>
       <c r="AN2">
-        <v>0.2313725490196079</v>
+        <v>0.06706827309236947</v>
       </c>
       <c r="AO2">
-        <v>26.42559109874826</v>
+        <v>2843.333333333333</v>
       </c>
       <c r="AP2">
-        <v>-0.7686274509803922</v>
+        <v>-3.808433734939759</v>
       </c>
       <c r="AQ2">
-        <v>26.42559109874826</v>
+        <v>2843.333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.231</v>
+        <v>0.177</v>
       </c>
       <c r="E3">
-        <v>0.248</v>
+        <v>0.205</v>
       </c>
       <c r="G3">
-        <v>0.2194381169324222</v>
+        <v>0.08828828828828829</v>
       </c>
       <c r="H3">
-        <v>0.2194381169324222</v>
+        <v>0.08828828828828829</v>
       </c>
       <c r="I3">
-        <v>0.1442672741078208</v>
+        <v>0.07684684684684684</v>
       </c>
       <c r="J3">
-        <v>0.1207918300961932</v>
+        <v>0.06301441441441441</v>
       </c>
       <c r="K3">
-        <v>9.33</v>
+        <v>12.3</v>
       </c>
       <c r="L3">
-        <v>0.07084282460136675</v>
+        <v>0.1108108108108108</v>
       </c>
       <c r="M3">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>0.02156521739130435</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="O3">
-        <v>0.1329046087888532</v>
+        <v>0.08943089430894309</v>
       </c>
       <c r="P3">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="Q3">
-        <v>0.02156521739130435</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="R3">
-        <v>0.1329046087888532</v>
+        <v>0.08943089430894309</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>20.4</v>
+        <v>38.6</v>
       </c>
       <c r="V3">
-        <v>0.3547826086956521</v>
+        <v>1.131964809384164</v>
       </c>
       <c r="W3">
-        <v>0.08835227272727274</v>
+        <v>0.1754636233951498</v>
       </c>
       <c r="X3">
-        <v>0.2656539013594726</v>
+        <v>0.1906774660719821</v>
       </c>
       <c r="Y3">
-        <v>-0.1773016286321999</v>
+        <v>-0.01521384267683232</v>
       </c>
       <c r="Z3">
-        <v>1.789645332246229</v>
+        <v>2.039691289966924</v>
       </c>
       <c r="AA3">
-        <v>0.2161745349051316</v>
+        <v>0.1285299522234473</v>
       </c>
       <c r="AB3">
-        <v>0.2565462865225929</v>
+        <v>0.1893554156546594</v>
       </c>
       <c r="AC3">
-        <v>-0.04037175161746129</v>
+        <v>-0.06082546343121206</v>
       </c>
       <c r="AD3">
-        <v>4.72</v>
+        <v>0.668</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.72</v>
+        <v>0.668</v>
       </c>
       <c r="AG3">
-        <v>-15.68</v>
+        <v>-37.932</v>
       </c>
       <c r="AH3">
-        <v>0.07585985213757634</v>
+        <v>0.01921306948918546</v>
       </c>
       <c r="AI3">
-        <v>0.049569418189456</v>
+        <v>0.00693176158060767</v>
       </c>
       <c r="AJ3">
-        <v>-0.3749402199904352</v>
+        <v>9.898747390396659</v>
       </c>
       <c r="AK3">
-        <v>-0.2095696337877573</v>
+        <v>-0.6566265060240964</v>
       </c>
       <c r="AL3">
-        <v>0.719</v>
+        <v>0.003</v>
       </c>
       <c r="AM3">
-        <v>0.719</v>
+        <v>0.003</v>
       </c>
       <c r="AN3">
-        <v>0.2313725490196079</v>
+        <v>0.06706827309236947</v>
       </c>
       <c r="AO3">
-        <v>26.42559109874826</v>
+        <v>2843.333333333333</v>
       </c>
       <c r="AP3">
-        <v>-0.7686274509803922</v>
+        <v>-3.808433734939759</v>
       </c>
       <c r="AQ3">
-        <v>26.42559109874826</v>
+        <v>2843.333333333333</v>
       </c>
     </row>
   </sheetData>
